--- a/reports/history/build-5/Passed_Test_Cases.xlsx
+++ b/reports/history/build-5/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="1030">
   <si>
     <t>Test ID</t>
   </si>
@@ -301,6 +301,12 @@
     <t>Authorization Verification - Case 2</t>
   </si>
   <si>
+    <t>TC_AZ_003</t>
+  </si>
+  <si>
+    <t>Authorization Verification - Case 3</t>
+  </si>
+  <si>
     <t>TC_AZ_004</t>
   </si>
   <si>
@@ -697,12 +703,6 @@
     <t>Profile Management Verification - Case 18</t>
   </si>
   <si>
-    <t>TC_PROF_019</t>
-  </si>
-  <si>
-    <t>Profile Management Verification - Case 19</t>
-  </si>
-  <si>
     <t>TC_PROF_020</t>
   </si>
   <si>
@@ -814,6 +814,12 @@
     <t>Navigation Verification - Case 17</t>
   </si>
   <si>
+    <t>TC_NAV_018</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 18</t>
+  </si>
+  <si>
     <t>TC_NAV_019</t>
   </si>
   <si>
@@ -850,6 +856,12 @@
     <t>Navigation Verification - Case 24</t>
   </si>
   <si>
+    <t>TC_NAV_025</t>
+  </si>
+  <si>
+    <t>Navigation Verification - Case 25</t>
+  </si>
+  <si>
     <t>TC_NAV_026</t>
   </si>
   <si>
@@ -868,12 +880,6 @@
     <t>Navigation Verification - Case 28</t>
   </si>
   <si>
-    <t>TC_NAV_029</t>
-  </si>
-  <si>
-    <t>Navigation Verification - Case 29</t>
-  </si>
-  <si>
     <t>TC_NAV_030</t>
   </si>
   <si>
@@ -1096,12 +1102,6 @@
     <t>Forms Verification - Case 15</t>
   </si>
   <si>
-    <t>TC_FORM_016</t>
-  </si>
-  <si>
-    <t>Forms Verification - Case 16</t>
-  </si>
-  <si>
     <t>TC_FORM_017</t>
   </si>
   <si>
@@ -1192,6 +1192,12 @@
     <t>Forms Verification - Case 31</t>
   </si>
   <si>
+    <t>TC_FORM_032</t>
+  </si>
+  <si>
+    <t>Forms Verification - Case 32</t>
+  </si>
+  <si>
     <t>TC_FORM_033</t>
   </si>
   <si>
@@ -1255,12 +1261,6 @@
     <t>CRUD Operations Verification - Case 2</t>
   </si>
   <si>
-    <t>TC_CRUD_003</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 3</t>
-  </si>
-  <si>
     <t>TC_CRUD_004</t>
   </si>
   <si>
@@ -1351,12 +1351,6 @@
     <t>CRUD Operations Verification - Case 18</t>
   </si>
   <si>
-    <t>TC_CRUD_019</t>
-  </si>
-  <si>
-    <t>CRUD Operations Verification - Case 19</t>
-  </si>
-  <si>
     <t>TC_CRUD_020</t>
   </si>
   <si>
@@ -1399,6 +1393,12 @@
     <t>CRUD Operations Verification - Case 26</t>
   </si>
   <si>
+    <t>TC_CRUD_027</t>
+  </si>
+  <si>
+    <t>CRUD Operations Verification - Case 27</t>
+  </si>
+  <si>
     <t>TC_CRUD_028</t>
   </si>
   <si>
@@ -1528,12 +1528,6 @@
     <t>Search Verification - Case 8</t>
   </si>
   <si>
-    <t>TC_SRCH_009</t>
-  </si>
-  <si>
-    <t>Search Verification - Case 9</t>
-  </si>
-  <si>
     <t>TC_SRCH_010</t>
   </si>
   <si>
@@ -1651,18 +1645,6 @@
     <t>Filters Verification - Case 8</t>
   </si>
   <si>
-    <t>TC_FILT_009</t>
-  </si>
-  <si>
-    <t>Filters Verification - Case 9</t>
-  </si>
-  <si>
-    <t>TC_FILT_010</t>
-  </si>
-  <si>
-    <t>Filters Verification - Case 10</t>
-  </si>
-  <si>
     <t>TC_FILT_011</t>
   </si>
   <si>
@@ -2293,6 +2275,12 @@
     <t>Notifications Verification - Case 13</t>
   </si>
   <si>
+    <t>TC_NOTIF_014</t>
+  </si>
+  <si>
+    <t>Notifications Verification - Case 14</t>
+  </si>
+  <si>
     <t>TC_NOTIF_015</t>
   </si>
   <si>
@@ -2572,6 +2560,12 @@
     <t>Accessibility Verification - Case 9</t>
   </si>
   <si>
+    <t>TC_ACC_010</t>
+  </si>
+  <si>
+    <t>Accessibility Verification - Case 10</t>
+  </si>
+  <si>
     <t>TC_ACC_011</t>
   </si>
   <si>
@@ -2590,12 +2584,6 @@
     <t>Accessibility Verification - Case 13</t>
   </si>
   <si>
-    <t>TC_ACC_014</t>
-  </si>
-  <si>
-    <t>Accessibility Verification - Case 14</t>
-  </si>
-  <si>
     <t>TC_ACC_015</t>
   </si>
   <si>
@@ -2632,18 +2620,12 @@
     <t>Accessibility Verification - Case 20</t>
   </si>
   <si>
-    <t>TC_RESP_001</t>
+    <t>TC_RESP_002</t>
   </si>
   <si>
     <t>Responsive UI</t>
   </si>
   <si>
-    <t>Responsive UI Verification - Case 1</t>
-  </si>
-  <si>
-    <t>TC_RESP_002</t>
-  </si>
-  <si>
     <t>Responsive UI Verification - Case 2</t>
   </si>
   <si>
@@ -2776,6 +2758,12 @@
     <t>Performance Smoke Tests Verification - Case 13</t>
   </si>
   <si>
+    <t>TC_PERF_014</t>
+  </si>
+  <si>
+    <t>Performance Smoke Tests Verification - Case 14</t>
+  </si>
+  <si>
     <t>TC_PERF_015</t>
   </si>
   <si>
@@ -3035,6 +3023,12 @@
   </si>
   <si>
     <t>Regression Suite Verification - Case 37</t>
+  </si>
+  <si>
+    <t>TC_REGR_038</t>
+  </si>
+  <si>
+    <t>Regression Suite Verification - Case 38</t>
   </si>
   <si>
     <t>TC_REGR_039</t>
@@ -3497,7 +3491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F502"/>
+  <dimension ref="A1:F501"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3544,7 +3538,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>166</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3564,7 +3558,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>263</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3584,7 +3578,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3604,7 +3598,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3624,7 +3618,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>190</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3644,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3664,7 +3658,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>250</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3684,7 +3678,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>177</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3704,7 +3698,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>135</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3724,7 +3718,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>214</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3744,7 +3738,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3764,7 +3758,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>273</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3784,7 +3778,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>281</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -3804,7 +3798,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>101</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3824,7 +3818,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3844,7 +3838,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>218</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3864,7 +3858,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>230</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3884,7 +3878,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3904,7 +3898,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3924,7 +3918,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>295</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3944,7 +3938,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>239</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3964,7 +3958,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>185</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3984,7 +3978,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>213</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4004,7 +3998,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>237</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4024,7 +4018,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>193</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4044,7 +4038,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>109</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4064,7 +4058,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>242</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4084,7 +4078,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>122</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4104,7 +4098,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>136</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4124,7 +4118,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>279</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4144,7 +4138,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>216</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4164,7 +4158,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>144</v>
+        <v>206</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4184,7 +4178,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>206</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4204,7 +4198,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>123</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4224,7 +4218,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>241</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4244,7 +4238,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>239</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4264,7 +4258,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>183</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4284,7 +4278,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>168</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4304,7 +4298,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>135</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4324,7 +4318,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>254</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4344,7 +4338,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>285</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4364,7 +4358,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>240</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4378,13 +4372,13 @@
         <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4398,13 +4392,13 @@
         <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
       <c r="F45">
-        <v>194</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4418,13 +4412,13 @@
         <v>101</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4438,13 +4432,13 @@
         <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
       <c r="F47">
-        <v>272</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4458,13 +4452,13 @@
         <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48">
-        <v>137</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4478,13 +4472,13 @@
         <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
       </c>
       <c r="F49">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4498,13 +4492,13 @@
         <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
       </c>
       <c r="F50">
-        <v>292</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4518,13 +4512,13 @@
         <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4538,13 +4532,13 @@
         <v>113</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52">
-        <v>100</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4558,13 +4552,13 @@
         <v>115</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
       </c>
       <c r="F53">
-        <v>225</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4578,13 +4572,13 @@
         <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54">
-        <v>260</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4598,13 +4592,13 @@
         <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55">
-        <v>116</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4618,13 +4612,13 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
       </c>
       <c r="F56">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4638,13 +4632,13 @@
         <v>123</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
       </c>
       <c r="F57">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4658,13 +4652,13 @@
         <v>125</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
       </c>
       <c r="F58">
-        <v>228</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4678,13 +4672,13 @@
         <v>127</v>
       </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
       <c r="F59">
-        <v>169</v>
+        <v>138</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4698,13 +4692,13 @@
         <v>129</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60">
-        <v>101</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4718,13 +4712,13 @@
         <v>131</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
       </c>
       <c r="F61">
-        <v>262</v>
+        <v>225</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4738,13 +4732,13 @@
         <v>133</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62">
-        <v>178</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4758,13 +4752,13 @@
         <v>135</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="F63">
-        <v>127</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4778,13 +4772,13 @@
         <v>137</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
       </c>
       <c r="F64">
-        <v>281</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4798,13 +4792,13 @@
         <v>139</v>
       </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
       </c>
       <c r="F65">
-        <v>232</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4818,13 +4812,13 @@
         <v>141</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
       </c>
       <c r="F66">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -4838,13 +4832,13 @@
         <v>143</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
       </c>
       <c r="F67">
-        <v>157</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -4858,13 +4852,13 @@
         <v>145</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
       </c>
       <c r="F68">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -4878,13 +4872,13 @@
         <v>147</v>
       </c>
       <c r="D69" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
       </c>
       <c r="F69">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -4898,13 +4892,13 @@
         <v>149</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -4912,39 +4906,39 @@
         <v>150</v>
       </c>
       <c r="B71" t="s">
+        <v>92</v>
+      </c>
+      <c r="C71" t="s">
         <v>151</v>
       </c>
-      <c r="C71" t="s">
-        <v>152</v>
-      </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71">
-        <v>264</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" t="s">
         <v>153</v>
-      </c>
-      <c r="B72" t="s">
-        <v>151</v>
       </c>
       <c r="C72" t="s">
         <v>154</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
       </c>
       <c r="F72">
-        <v>198</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -4952,19 +4946,19 @@
         <v>155</v>
       </c>
       <c r="B73" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
         <v>156</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73">
-        <v>280</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -4972,19 +4966,19 @@
         <v>157</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
         <v>158</v>
       </c>
       <c r="D74" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74">
-        <v>200</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -4992,19 +4986,19 @@
         <v>159</v>
       </c>
       <c r="B75" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s">
         <v>160</v>
       </c>
       <c r="D75" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
       </c>
       <c r="F75">
-        <v>154</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5012,19 +5006,19 @@
         <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C76" t="s">
         <v>162</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
       </c>
       <c r="F76">
-        <v>174</v>
+        <v>243</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5032,19 +5026,19 @@
         <v>163</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
         <v>164</v>
       </c>
       <c r="D77" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
       </c>
       <c r="F77">
-        <v>105</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5052,19 +5046,19 @@
         <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
         <v>166</v>
       </c>
       <c r="D78" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
       <c r="F78">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5072,19 +5066,19 @@
         <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
         <v>168</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
       </c>
       <c r="F79">
-        <v>184</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5092,19 +5086,19 @@
         <v>169</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
         <v>170</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
       </c>
       <c r="F80">
-        <v>207</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5112,19 +5106,19 @@
         <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C81" t="s">
         <v>172</v>
       </c>
       <c r="D81" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
       </c>
       <c r="F81">
-        <v>116</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5132,19 +5126,19 @@
         <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
         <v>174</v>
       </c>
       <c r="D82" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82">
-        <v>146</v>
+        <v>279</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5152,19 +5146,19 @@
         <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
         <v>176</v>
       </c>
       <c r="D83" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
       </c>
       <c r="F83">
-        <v>152</v>
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5172,19 +5166,19 @@
         <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
         <v>178</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
       </c>
       <c r="F84">
-        <v>192</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5192,19 +5186,19 @@
         <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
         <v>180</v>
       </c>
       <c r="D85" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
       </c>
       <c r="F85">
-        <v>123</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5212,19 +5206,19 @@
         <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C86" t="s">
         <v>182</v>
       </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86">
-        <v>224</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5232,19 +5226,19 @@
         <v>183</v>
       </c>
       <c r="B87" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C87" t="s">
         <v>184</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
       </c>
       <c r="F87">
-        <v>225</v>
+        <v>294</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5252,19 +5246,19 @@
         <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C88" t="s">
         <v>186</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
       </c>
       <c r="F88">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5272,19 +5266,19 @@
         <v>187</v>
       </c>
       <c r="B89" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C89" t="s">
         <v>188</v>
       </c>
       <c r="D89" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
       </c>
       <c r="F89">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5292,19 +5286,19 @@
         <v>189</v>
       </c>
       <c r="B90" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C90" t="s">
         <v>190</v>
       </c>
       <c r="D90" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
       </c>
       <c r="F90">
-        <v>290</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -5312,39 +5306,39 @@
         <v>191</v>
       </c>
       <c r="B91" t="s">
+        <v>153</v>
+      </c>
+      <c r="C91" t="s">
         <v>192</v>
       </c>
-      <c r="C91" t="s">
-        <v>193</v>
-      </c>
       <c r="D91" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
       </c>
       <c r="F91">
-        <v>205</v>
+        <v>264</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>193</v>
+      </c>
+      <c r="B92" t="s">
         <v>194</v>
-      </c>
-      <c r="B92" t="s">
-        <v>192</v>
       </c>
       <c r="C92" t="s">
         <v>195</v>
       </c>
       <c r="D92" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
       </c>
       <c r="F92">
-        <v>107</v>
+        <v>257</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5352,19 +5346,19 @@
         <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
         <v>197</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
       </c>
       <c r="F93">
-        <v>117</v>
+        <v>256</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5372,19 +5366,19 @@
         <v>198</v>
       </c>
       <c r="B94" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C94" t="s">
         <v>199</v>
       </c>
       <c r="D94" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
       </c>
       <c r="F94">
-        <v>238</v>
+        <v>278</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5392,19 +5386,19 @@
         <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C95" t="s">
         <v>201</v>
       </c>
       <c r="D95" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
       </c>
       <c r="F95">
-        <v>127</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5412,19 +5406,19 @@
         <v>202</v>
       </c>
       <c r="B96" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
         <v>203</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
       </c>
       <c r="F96">
-        <v>252</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5432,19 +5426,19 @@
         <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C97" t="s">
         <v>205</v>
       </c>
       <c r="D97" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
       </c>
       <c r="F97">
-        <v>265</v>
+        <v>130</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5452,19 +5446,19 @@
         <v>206</v>
       </c>
       <c r="B98" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C98" t="s">
         <v>207</v>
       </c>
       <c r="D98" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
       </c>
       <c r="F98">
-        <v>201</v>
+        <v>102</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5472,19 +5466,19 @@
         <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C99" t="s">
         <v>209</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E99" t="s">
         <v>10</v>
       </c>
       <c r="F99">
-        <v>295</v>
+        <v>283</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5492,19 +5486,19 @@
         <v>210</v>
       </c>
       <c r="B100" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C100" t="s">
         <v>211</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E100" t="s">
         <v>10</v>
       </c>
       <c r="F100">
-        <v>114</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5512,19 +5506,19 @@
         <v>212</v>
       </c>
       <c r="B101" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C101" t="s">
         <v>213</v>
       </c>
       <c r="D101" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
       </c>
       <c r="F101">
-        <v>107</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5532,19 +5526,19 @@
         <v>214</v>
       </c>
       <c r="B102" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C102" t="s">
         <v>215</v>
       </c>
       <c r="D102" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
       </c>
       <c r="F102">
-        <v>238</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5552,19 +5546,19 @@
         <v>216</v>
       </c>
       <c r="B103" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C103" t="s">
         <v>217</v>
       </c>
       <c r="D103" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
       </c>
       <c r="F103">
-        <v>204</v>
+        <v>169</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5572,19 +5566,19 @@
         <v>218</v>
       </c>
       <c r="B104" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C104" t="s">
         <v>219</v>
       </c>
       <c r="D104" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
       </c>
       <c r="F104">
-        <v>212</v>
+        <v>298</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5592,19 +5586,19 @@
         <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C105" t="s">
         <v>221</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
       </c>
       <c r="F105">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5612,19 +5606,19 @@
         <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C106" t="s">
         <v>223</v>
       </c>
       <c r="D106" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
       </c>
       <c r="F106">
-        <v>121</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5632,19 +5626,19 @@
         <v>224</v>
       </c>
       <c r="B107" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C107" t="s">
         <v>225</v>
       </c>
       <c r="D107" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
       </c>
       <c r="F107">
-        <v>225</v>
+        <v>283</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5652,19 +5646,19 @@
         <v>226</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C108" t="s">
         <v>227</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E108" t="s">
         <v>10</v>
       </c>
       <c r="F108">
-        <v>154</v>
+        <v>284</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -5672,19 +5666,19 @@
         <v>228</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C109" t="s">
         <v>229</v>
       </c>
       <c r="D109" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E109" t="s">
         <v>10</v>
       </c>
       <c r="F109">
-        <v>233</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -5692,7 +5686,7 @@
         <v>230</v>
       </c>
       <c r="B110" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C110" t="s">
         <v>231</v>
@@ -5704,7 +5698,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5724,7 +5718,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -5744,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>198</v>
+        <v>295</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -5764,7 +5758,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>295</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5784,7 +5778,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>225</v>
+        <v>189</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -5804,7 +5798,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>263</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -5824,7 +5818,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>273</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -5844,7 +5838,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>230</v>
+        <v>184</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -5864,7 +5858,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>147</v>
+        <v>239</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -5884,7 +5878,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>178</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -5904,7 +5898,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>267</v>
+        <v>187</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -5924,7 +5918,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>281</v>
+        <v>134</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -5944,7 +5938,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -5964,7 +5958,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>134</v>
+        <v>283</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -5984,7 +5978,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>106</v>
+        <v>206</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -6004,7 +5998,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>196</v>
+        <v>226</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -6024,7 +6018,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6044,7 +6038,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>110</v>
+        <v>162</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6058,13 +6052,13 @@
         <v>268</v>
       </c>
       <c r="D128" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
       </c>
       <c r="F128">
-        <v>292</v>
+        <v>183</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6078,13 +6072,13 @@
         <v>270</v>
       </c>
       <c r="D129" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E129" t="s">
         <v>10</v>
       </c>
       <c r="F129">
-        <v>208</v>
+        <v>144</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6098,13 +6092,13 @@
         <v>272</v>
       </c>
       <c r="D130" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
       </c>
       <c r="F130">
-        <v>215</v>
+        <v>167</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6118,13 +6112,13 @@
         <v>274</v>
       </c>
       <c r="D131" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
       </c>
       <c r="F131">
-        <v>242</v>
+        <v>206</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6138,13 +6132,13 @@
         <v>276</v>
       </c>
       <c r="D132" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
       </c>
       <c r="F132">
-        <v>291</v>
+        <v>126</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6158,13 +6152,13 @@
         <v>278</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
       </c>
       <c r="F133">
-        <v>178</v>
+        <v>296</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6178,13 +6172,13 @@
         <v>280</v>
       </c>
       <c r="D134" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
       </c>
       <c r="F134">
-        <v>154</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6198,13 +6192,13 @@
         <v>282</v>
       </c>
       <c r="D135" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
       </c>
       <c r="F135">
-        <v>201</v>
+        <v>267</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6218,13 +6212,13 @@
         <v>284</v>
       </c>
       <c r="D136" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
       </c>
       <c r="F136">
-        <v>265</v>
+        <v>242</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6238,13 +6232,13 @@
         <v>286</v>
       </c>
       <c r="D137" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
       </c>
       <c r="F137">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6258,13 +6252,13 @@
         <v>288</v>
       </c>
       <c r="D138" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
       </c>
       <c r="F138">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -6272,39 +6266,39 @@
         <v>289</v>
       </c>
       <c r="B139" t="s">
+        <v>233</v>
+      </c>
+      <c r="C139" t="s">
         <v>290</v>
       </c>
-      <c r="C139" t="s">
-        <v>291</v>
-      </c>
       <c r="D139" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
       </c>
       <c r="F139">
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>291</v>
+      </c>
+      <c r="B140" t="s">
         <v>292</v>
-      </c>
-      <c r="B140" t="s">
-        <v>290</v>
       </c>
       <c r="C140" t="s">
         <v>293</v>
       </c>
       <c r="D140" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
       </c>
       <c r="F140">
-        <v>148</v>
+        <v>216</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6312,19 +6306,19 @@
         <v>294</v>
       </c>
       <c r="B141" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C141" t="s">
         <v>295</v>
       </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
       </c>
       <c r="F141">
-        <v>160</v>
+        <v>229</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6332,19 +6326,19 @@
         <v>296</v>
       </c>
       <c r="B142" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C142" t="s">
         <v>297</v>
       </c>
       <c r="D142" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
       </c>
       <c r="F142">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -6352,19 +6346,19 @@
         <v>298</v>
       </c>
       <c r="B143" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C143" t="s">
         <v>299</v>
       </c>
       <c r="D143" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E143" t="s">
         <v>10</v>
       </c>
       <c r="F143">
-        <v>175</v>
+        <v>239</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6372,19 +6366,19 @@
         <v>300</v>
       </c>
       <c r="B144" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C144" t="s">
         <v>301</v>
       </c>
       <c r="D144" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E144" t="s">
         <v>10</v>
       </c>
       <c r="F144">
-        <v>100</v>
+        <v>280</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6392,19 +6386,19 @@
         <v>302</v>
       </c>
       <c r="B145" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C145" t="s">
         <v>303</v>
       </c>
       <c r="D145" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E145" t="s">
         <v>10</v>
       </c>
       <c r="F145">
-        <v>181</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6412,19 +6406,19 @@
         <v>304</v>
       </c>
       <c r="B146" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C146" t="s">
         <v>305</v>
       </c>
       <c r="D146" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E146" t="s">
         <v>10</v>
       </c>
       <c r="F146">
-        <v>178</v>
+        <v>141</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6432,19 +6426,19 @@
         <v>306</v>
       </c>
       <c r="B147" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C147" t="s">
         <v>307</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
       </c>
       <c r="F147">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6452,19 +6446,19 @@
         <v>308</v>
       </c>
       <c r="B148" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C148" t="s">
         <v>309</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
       </c>
       <c r="F148">
-        <v>295</v>
+        <v>161</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6472,19 +6466,19 @@
         <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C149" t="s">
         <v>311</v>
       </c>
       <c r="D149" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
       </c>
       <c r="F149">
-        <v>130</v>
+        <v>298</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6492,19 +6486,19 @@
         <v>312</v>
       </c>
       <c r="B150" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C150" t="s">
         <v>313</v>
       </c>
       <c r="D150" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
       </c>
       <c r="F150">
-        <v>102</v>
+        <v>256</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6512,19 +6506,19 @@
         <v>314</v>
       </c>
       <c r="B151" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C151" t="s">
         <v>315</v>
       </c>
       <c r="D151" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
       </c>
       <c r="F151">
-        <v>253</v>
+        <v>277</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6532,19 +6526,19 @@
         <v>316</v>
       </c>
       <c r="B152" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C152" t="s">
         <v>317</v>
       </c>
       <c r="D152" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
       </c>
       <c r="F152">
-        <v>218</v>
+        <v>152</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6552,19 +6546,19 @@
         <v>318</v>
       </c>
       <c r="B153" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C153" t="s">
         <v>319</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E153" t="s">
         <v>10</v>
       </c>
       <c r="F153">
-        <v>267</v>
+        <v>118</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6572,19 +6566,19 @@
         <v>320</v>
       </c>
       <c r="B154" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C154" t="s">
         <v>321</v>
       </c>
       <c r="D154" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E154" t="s">
         <v>10</v>
       </c>
       <c r="F154">
-        <v>208</v>
+        <v>267</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6592,19 +6586,19 @@
         <v>322</v>
       </c>
       <c r="B155" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C155" t="s">
         <v>323</v>
       </c>
       <c r="D155" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
         <v>10</v>
       </c>
       <c r="F155">
-        <v>195</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6612,19 +6606,19 @@
         <v>324</v>
       </c>
       <c r="B156" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C156" t="s">
         <v>325</v>
       </c>
       <c r="D156" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
       </c>
       <c r="F156">
-        <v>282</v>
+        <v>239</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6632,19 +6626,19 @@
         <v>326</v>
       </c>
       <c r="B157" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C157" t="s">
         <v>327</v>
       </c>
       <c r="D157" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E157" t="s">
         <v>10</v>
       </c>
       <c r="F157">
-        <v>297</v>
+        <v>116</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6652,19 +6646,19 @@
         <v>328</v>
       </c>
       <c r="B158" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C158" t="s">
         <v>329</v>
       </c>
       <c r="D158" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
       </c>
       <c r="F158">
-        <v>117</v>
+        <v>147</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -6672,39 +6666,39 @@
         <v>330</v>
       </c>
       <c r="B159" t="s">
+        <v>292</v>
+      </c>
+      <c r="C159" t="s">
         <v>331</v>
       </c>
-      <c r="C159" t="s">
-        <v>332</v>
-      </c>
       <c r="D159" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E159" t="s">
         <v>10</v>
       </c>
       <c r="F159">
-        <v>119</v>
+        <v>157</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>332</v>
+      </c>
+      <c r="B160" t="s">
         <v>333</v>
-      </c>
-      <c r="B160" t="s">
-        <v>331</v>
       </c>
       <c r="C160" t="s">
         <v>334</v>
       </c>
       <c r="D160" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E160" t="s">
         <v>10</v>
       </c>
       <c r="F160">
-        <v>283</v>
+        <v>146</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6712,19 +6706,19 @@
         <v>335</v>
       </c>
       <c r="B161" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C161" t="s">
         <v>336</v>
       </c>
       <c r="D161" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161">
-        <v>186</v>
+        <v>120</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6732,19 +6726,19 @@
         <v>337</v>
       </c>
       <c r="B162" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C162" t="s">
         <v>338</v>
       </c>
       <c r="D162" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E162" t="s">
         <v>10</v>
       </c>
       <c r="F162">
-        <v>245</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -6752,19 +6746,19 @@
         <v>339</v>
       </c>
       <c r="B163" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C163" t="s">
         <v>340</v>
       </c>
       <c r="D163" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
       </c>
       <c r="F163">
-        <v>213</v>
+        <v>262</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -6772,19 +6766,19 @@
         <v>341</v>
       </c>
       <c r="B164" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C164" t="s">
         <v>342</v>
       </c>
       <c r="D164" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
       </c>
       <c r="F164">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -6792,19 +6786,19 @@
         <v>343</v>
       </c>
       <c r="B165" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C165" t="s">
         <v>344</v>
       </c>
       <c r="D165" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
       </c>
       <c r="F165">
-        <v>143</v>
+        <v>288</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -6812,19 +6806,19 @@
         <v>345</v>
       </c>
       <c r="B166" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C166" t="s">
         <v>346</v>
       </c>
       <c r="D166" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
       </c>
       <c r="F166">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6832,19 +6826,19 @@
         <v>347</v>
       </c>
       <c r="B167" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C167" t="s">
         <v>348</v>
       </c>
       <c r="D167" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
       </c>
       <c r="F167">
-        <v>265</v>
+        <v>219</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -6852,19 +6846,19 @@
         <v>349</v>
       </c>
       <c r="B168" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C168" t="s">
         <v>350</v>
       </c>
       <c r="D168" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E168" t="s">
         <v>10</v>
       </c>
       <c r="F168">
-        <v>238</v>
+        <v>296</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -6872,19 +6866,19 @@
         <v>351</v>
       </c>
       <c r="B169" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C169" t="s">
         <v>352</v>
       </c>
       <c r="D169" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
       </c>
       <c r="F169">
-        <v>229</v>
+        <v>100</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -6892,19 +6886,19 @@
         <v>353</v>
       </c>
       <c r="B170" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C170" t="s">
         <v>354</v>
       </c>
       <c r="D170" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
       </c>
       <c r="F170">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -6912,19 +6906,19 @@
         <v>355</v>
       </c>
       <c r="B171" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C171" t="s">
         <v>356</v>
       </c>
       <c r="D171" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E171" t="s">
         <v>10</v>
       </c>
       <c r="F171">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -6932,19 +6926,19 @@
         <v>357</v>
       </c>
       <c r="B172" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C172" t="s">
         <v>358</v>
       </c>
       <c r="D172" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
       </c>
       <c r="F172">
-        <v>299</v>
+        <v>212</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -6952,19 +6946,19 @@
         <v>359</v>
       </c>
       <c r="B173" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C173" t="s">
         <v>360</v>
       </c>
       <c r="D173" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E173" t="s">
         <v>10</v>
       </c>
       <c r="F173">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -6972,19 +6966,19 @@
         <v>361</v>
       </c>
       <c r="B174" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C174" t="s">
         <v>362</v>
       </c>
       <c r="D174" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E174" t="s">
         <v>10</v>
       </c>
       <c r="F174">
-        <v>296</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -6992,7 +6986,7 @@
         <v>363</v>
       </c>
       <c r="B175" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C175" t="s">
         <v>364</v>
@@ -7004,7 +6998,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>263</v>
+        <v>168</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -7012,7 +7006,7 @@
         <v>365</v>
       </c>
       <c r="B176" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C176" t="s">
         <v>366</v>
@@ -7024,7 +7018,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7032,7 +7026,7 @@
         <v>367</v>
       </c>
       <c r="B177" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C177" t="s">
         <v>368</v>
@@ -7044,7 +7038,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>279</v>
+        <v>141</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7052,7 +7046,7 @@
         <v>369</v>
       </c>
       <c r="B178" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C178" t="s">
         <v>370</v>
@@ -7064,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>133</v>
+        <v>268</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7072,7 +7066,7 @@
         <v>371</v>
       </c>
       <c r="B179" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C179" t="s">
         <v>372</v>
@@ -7084,7 +7078,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>245</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7092,7 +7086,7 @@
         <v>373</v>
       </c>
       <c r="B180" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C180" t="s">
         <v>374</v>
@@ -7104,7 +7098,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>192</v>
+        <v>233</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7112,7 +7106,7 @@
         <v>375</v>
       </c>
       <c r="B181" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C181" t="s">
         <v>376</v>
@@ -7124,7 +7118,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>254</v>
+        <v>154</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7132,7 +7126,7 @@
         <v>377</v>
       </c>
       <c r="B182" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C182" t="s">
         <v>378</v>
@@ -7144,7 +7138,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>298</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7152,7 +7146,7 @@
         <v>379</v>
       </c>
       <c r="B183" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C183" t="s">
         <v>380</v>
@@ -7164,7 +7158,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>269</v>
+        <v>206</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7172,7 +7166,7 @@
         <v>381</v>
       </c>
       <c r="B184" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C184" t="s">
         <v>382</v>
@@ -7184,7 +7178,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>221</v>
+        <v>237</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7192,7 +7186,7 @@
         <v>383</v>
       </c>
       <c r="B185" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C185" t="s">
         <v>384</v>
@@ -7204,7 +7198,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>214</v>
+        <v>191</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -7212,7 +7206,7 @@
         <v>385</v>
       </c>
       <c r="B186" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C186" t="s">
         <v>386</v>
@@ -7224,7 +7218,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>240</v>
+        <v>293</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7232,7 +7226,7 @@
         <v>387</v>
       </c>
       <c r="B187" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C187" t="s">
         <v>388</v>
@@ -7244,7 +7238,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>284</v>
+        <v>129</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7252,7 +7246,7 @@
         <v>389</v>
       </c>
       <c r="B188" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C188" t="s">
         <v>390</v>
@@ -7264,7 +7258,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>264</v>
+        <v>143</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7272,7 +7266,7 @@
         <v>391</v>
       </c>
       <c r="B189" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C189" t="s">
         <v>392</v>
@@ -7284,7 +7278,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>115</v>
+        <v>229</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7292,19 +7286,19 @@
         <v>393</v>
       </c>
       <c r="B190" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C190" t="s">
         <v>394</v>
       </c>
       <c r="D190" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E190" t="s">
         <v>10</v>
       </c>
       <c r="F190">
-        <v>108</v>
+        <v>130</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7312,19 +7306,19 @@
         <v>395</v>
       </c>
       <c r="B191" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C191" t="s">
         <v>396</v>
       </c>
       <c r="D191" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E191" t="s">
         <v>10</v>
       </c>
       <c r="F191">
-        <v>205</v>
+        <v>262</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7332,19 +7326,19 @@
         <v>397</v>
       </c>
       <c r="B192" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C192" t="s">
         <v>398</v>
       </c>
       <c r="D192" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E192" t="s">
         <v>10</v>
       </c>
       <c r="F192">
-        <v>255</v>
+        <v>142</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7352,19 +7346,19 @@
         <v>399</v>
       </c>
       <c r="B193" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C193" t="s">
         <v>400</v>
       </c>
       <c r="D193" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E193" t="s">
         <v>10</v>
       </c>
       <c r="F193">
-        <v>245</v>
+        <v>214</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7372,19 +7366,19 @@
         <v>401</v>
       </c>
       <c r="B194" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C194" t="s">
         <v>402</v>
       </c>
       <c r="D194" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E194" t="s">
         <v>10</v>
       </c>
       <c r="F194">
-        <v>199</v>
+        <v>289</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7392,19 +7386,19 @@
         <v>403</v>
       </c>
       <c r="B195" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C195" t="s">
         <v>404</v>
       </c>
       <c r="D195" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E195" t="s">
         <v>10</v>
       </c>
       <c r="F195">
-        <v>125</v>
+        <v>280</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7412,19 +7406,19 @@
         <v>405</v>
       </c>
       <c r="B196" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C196" t="s">
         <v>406</v>
       </c>
       <c r="D196" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E196" t="s">
         <v>10</v>
       </c>
       <c r="F196">
-        <v>280</v>
+        <v>190</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7432,19 +7426,19 @@
         <v>407</v>
       </c>
       <c r="B197" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C197" t="s">
         <v>408</v>
       </c>
       <c r="D197" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E197" t="s">
         <v>10</v>
       </c>
       <c r="F197">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7452,11 +7446,11 @@
         <v>409</v>
       </c>
       <c r="B198" t="s">
+        <v>333</v>
+      </c>
+      <c r="C198" t="s">
         <v>410</v>
       </c>
-      <c r="C198" t="s">
-        <v>411</v>
-      </c>
       <c r="D198" t="s">
         <v>9</v>
       </c>
@@ -7464,27 +7458,27 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>148</v>
+        <v>270</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>411</v>
+      </c>
+      <c r="B199" t="s">
         <v>412</v>
-      </c>
-      <c r="B199" t="s">
-        <v>410</v>
       </c>
       <c r="C199" t="s">
         <v>413</v>
       </c>
       <c r="D199" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
       </c>
       <c r="F199">
-        <v>219</v>
+        <v>169</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7492,19 +7486,19 @@
         <v>414</v>
       </c>
       <c r="B200" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C200" t="s">
         <v>415</v>
       </c>
       <c r="D200" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E200" t="s">
         <v>10</v>
       </c>
       <c r="F200">
-        <v>112</v>
+        <v>154</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7512,7 +7506,7 @@
         <v>416</v>
       </c>
       <c r="B201" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C201" t="s">
         <v>417</v>
@@ -7524,7 +7518,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>299</v>
+        <v>166</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7532,7 +7526,7 @@
         <v>418</v>
       </c>
       <c r="B202" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C202" t="s">
         <v>419</v>
@@ -7544,7 +7538,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>265</v>
+        <v>153</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7552,7 +7546,7 @@
         <v>420</v>
       </c>
       <c r="B203" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C203" t="s">
         <v>421</v>
@@ -7564,7 +7558,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>185</v>
+        <v>273</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7572,7 +7566,7 @@
         <v>422</v>
       </c>
       <c r="B204" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C204" t="s">
         <v>423</v>
@@ -7584,7 +7578,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>266</v>
+        <v>100</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7592,7 +7586,7 @@
         <v>424</v>
       </c>
       <c r="B205" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C205" t="s">
         <v>425</v>
@@ -7604,7 +7598,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>299</v>
+        <v>287</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7612,7 +7606,7 @@
         <v>426</v>
       </c>
       <c r="B206" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C206" t="s">
         <v>427</v>
@@ -7624,7 +7618,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>111</v>
+        <v>293</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7632,7 +7626,7 @@
         <v>428</v>
       </c>
       <c r="B207" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C207" t="s">
         <v>429</v>
@@ -7644,7 +7638,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>162</v>
+        <v>240</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7652,7 +7646,7 @@
         <v>430</v>
       </c>
       <c r="B208" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C208" t="s">
         <v>431</v>
@@ -7664,7 +7658,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>167</v>
+        <v>274</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7672,7 +7666,7 @@
         <v>432</v>
       </c>
       <c r="B209" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C209" t="s">
         <v>433</v>
@@ -7684,7 +7678,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>276</v>
+        <v>123</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7692,7 +7686,7 @@
         <v>434</v>
       </c>
       <c r="B210" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C210" t="s">
         <v>435</v>
@@ -7704,7 +7698,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>277</v>
+        <v>194</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7712,7 +7706,7 @@
         <v>436</v>
       </c>
       <c r="B211" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C211" t="s">
         <v>437</v>
@@ -7724,7 +7718,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>283</v>
+        <v>223</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7732,7 +7726,7 @@
         <v>438</v>
       </c>
       <c r="B212" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C212" t="s">
         <v>439</v>
@@ -7744,7 +7738,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>286</v>
+        <v>189</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -7752,7 +7746,7 @@
         <v>440</v>
       </c>
       <c r="B213" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C213" t="s">
         <v>441</v>
@@ -7764,7 +7758,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>288</v>
+        <v>193</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -7772,7 +7766,7 @@
         <v>442</v>
       </c>
       <c r="B214" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C214" t="s">
         <v>443</v>
@@ -7784,7 +7778,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7792,7 +7786,7 @@
         <v>444</v>
       </c>
       <c r="B215" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C215" t="s">
         <v>445</v>
@@ -7804,7 +7798,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>268</v>
+        <v>145</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -7812,19 +7806,19 @@
         <v>446</v>
       </c>
       <c r="B216" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C216" t="s">
         <v>447</v>
       </c>
       <c r="D216" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E216" t="s">
         <v>10</v>
       </c>
       <c r="F216">
-        <v>205</v>
+        <v>144</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -7832,19 +7826,19 @@
         <v>448</v>
       </c>
       <c r="B217" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C217" t="s">
         <v>449</v>
       </c>
       <c r="D217" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E217" t="s">
         <v>10</v>
       </c>
       <c r="F217">
-        <v>236</v>
+        <v>151</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7852,19 +7846,19 @@
         <v>450</v>
       </c>
       <c r="B218" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C218" t="s">
         <v>451</v>
       </c>
       <c r="D218" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
       </c>
       <c r="F218">
-        <v>291</v>
+        <v>248</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -7872,19 +7866,19 @@
         <v>452</v>
       </c>
       <c r="B219" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C219" t="s">
         <v>453</v>
       </c>
       <c r="D219" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E219" t="s">
         <v>10</v>
       </c>
       <c r="F219">
-        <v>226</v>
+        <v>137</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -7892,19 +7886,19 @@
         <v>454</v>
       </c>
       <c r="B220" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C220" t="s">
         <v>455</v>
       </c>
       <c r="D220" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E220" t="s">
         <v>10</v>
       </c>
       <c r="F220">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -7912,19 +7906,19 @@
         <v>456</v>
       </c>
       <c r="B221" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C221" t="s">
         <v>457</v>
       </c>
       <c r="D221" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E221" t="s">
         <v>10</v>
       </c>
       <c r="F221">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -7932,19 +7926,19 @@
         <v>458</v>
       </c>
       <c r="B222" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C222" t="s">
         <v>459</v>
       </c>
       <c r="D222" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E222" t="s">
         <v>10</v>
       </c>
       <c r="F222">
-        <v>197</v>
+        <v>214</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7952,19 +7946,19 @@
         <v>460</v>
       </c>
       <c r="B223" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C223" t="s">
         <v>461</v>
       </c>
       <c r="D223" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E223" t="s">
         <v>10</v>
       </c>
       <c r="F223">
-        <v>299</v>
+        <v>114</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7972,7 +7966,7 @@
         <v>462</v>
       </c>
       <c r="B224" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C224" t="s">
         <v>463</v>
@@ -7984,7 +7978,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>254</v>
+        <v>184</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -7992,7 +7986,7 @@
         <v>464</v>
       </c>
       <c r="B225" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C225" t="s">
         <v>465</v>
@@ -8004,7 +7998,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8012,7 +8006,7 @@
         <v>466</v>
       </c>
       <c r="B226" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C226" t="s">
         <v>467</v>
@@ -8024,7 +8018,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>196</v>
+        <v>104</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8032,7 +8026,7 @@
         <v>468</v>
       </c>
       <c r="B227" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C227" t="s">
         <v>469</v>
@@ -8044,7 +8038,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>167</v>
+        <v>290</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8052,7 +8046,7 @@
         <v>470</v>
       </c>
       <c r="B228" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C228" t="s">
         <v>471</v>
@@ -8064,7 +8058,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>209</v>
+        <v>255</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8072,7 +8066,7 @@
         <v>472</v>
       </c>
       <c r="B229" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C229" t="s">
         <v>473</v>
@@ -8084,7 +8078,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>273</v>
+        <v>113</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -8092,7 +8086,7 @@
         <v>474</v>
       </c>
       <c r="B230" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C230" t="s">
         <v>475</v>
@@ -8104,7 +8098,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8112,7 +8106,7 @@
         <v>476</v>
       </c>
       <c r="B231" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C231" t="s">
         <v>477</v>
@@ -8124,7 +8118,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>209</v>
+        <v>282</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8132,7 +8126,7 @@
         <v>478</v>
       </c>
       <c r="B232" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C232" t="s">
         <v>479</v>
@@ -8144,7 +8138,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8152,7 +8146,7 @@
         <v>480</v>
       </c>
       <c r="B233" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C233" t="s">
         <v>481</v>
@@ -8164,7 +8158,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>194</v>
+        <v>101</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8172,7 +8166,7 @@
         <v>482</v>
       </c>
       <c r="B234" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C234" t="s">
         <v>483</v>
@@ -8184,7 +8178,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8192,7 +8186,7 @@
         <v>484</v>
       </c>
       <c r="B235" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C235" t="s">
         <v>485</v>
@@ -8204,7 +8198,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>258</v>
+        <v>132</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -8212,7 +8206,7 @@
         <v>486</v>
       </c>
       <c r="B236" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C236" t="s">
         <v>487</v>
@@ -8224,7 +8218,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>175</v>
+        <v>148</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -8244,7 +8238,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>221</v>
+        <v>117</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8284,7 +8278,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8304,7 +8298,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>197</v>
+        <v>117</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8324,7 +8318,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>289</v>
+        <v>112</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8344,7 +8338,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>138</v>
+        <v>192</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8364,7 +8358,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8384,7 +8378,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8398,13 +8392,13 @@
         <v>506</v>
       </c>
       <c r="D245" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E245" t="s">
         <v>10</v>
       </c>
       <c r="F245">
-        <v>102</v>
+        <v>238</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8418,13 +8412,13 @@
         <v>508</v>
       </c>
       <c r="D246" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E246" t="s">
         <v>10</v>
       </c>
       <c r="F246">
-        <v>157</v>
+        <v>102</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8438,13 +8432,13 @@
         <v>510</v>
       </c>
       <c r="D247" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E247" t="s">
         <v>10</v>
       </c>
       <c r="F247">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8458,13 +8452,13 @@
         <v>512</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E248" t="s">
         <v>10</v>
       </c>
       <c r="F248">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8478,13 +8472,13 @@
         <v>514</v>
       </c>
       <c r="D249" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E249" t="s">
         <v>10</v>
       </c>
       <c r="F249">
-        <v>141</v>
+        <v>275</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8498,13 +8492,13 @@
         <v>516</v>
       </c>
       <c r="D250" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E250" t="s">
         <v>10</v>
       </c>
       <c r="F250">
-        <v>102</v>
+        <v>130</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8518,13 +8512,13 @@
         <v>518</v>
       </c>
       <c r="D251" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E251" t="s">
         <v>10</v>
       </c>
       <c r="F251">
-        <v>276</v>
+        <v>148</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8538,13 +8532,13 @@
         <v>520</v>
       </c>
       <c r="D252" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E252" t="s">
         <v>10</v>
       </c>
       <c r="F252">
-        <v>207</v>
+        <v>223</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8558,13 +8552,13 @@
         <v>522</v>
       </c>
       <c r="D253" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E253" t="s">
         <v>10</v>
       </c>
       <c r="F253">
-        <v>284</v>
+        <v>112</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8578,13 +8572,13 @@
         <v>524</v>
       </c>
       <c r="D254" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E254" t="s">
         <v>10</v>
       </c>
       <c r="F254">
-        <v>201</v>
+        <v>267</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8598,13 +8592,13 @@
         <v>526</v>
       </c>
       <c r="D255" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E255" t="s">
         <v>10</v>
       </c>
       <c r="F255">
-        <v>171</v>
+        <v>299</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8612,39 +8606,39 @@
         <v>527</v>
       </c>
       <c r="B256" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="C256" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D256" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E256" t="s">
         <v>10</v>
       </c>
       <c r="F256">
-        <v>263</v>
+        <v>161</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B257" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C257" t="s">
         <v>531</v>
       </c>
       <c r="D257" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E257" t="s">
         <v>10</v>
       </c>
       <c r="F257">
-        <v>119</v>
+        <v>235</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8652,19 +8646,19 @@
         <v>532</v>
       </c>
       <c r="B258" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C258" t="s">
         <v>533</v>
       </c>
       <c r="D258" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E258" t="s">
         <v>10</v>
       </c>
       <c r="F258">
-        <v>208</v>
+        <v>152</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8672,19 +8666,19 @@
         <v>534</v>
       </c>
       <c r="B259" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C259" t="s">
         <v>535</v>
       </c>
       <c r="D259" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E259" t="s">
         <v>10</v>
       </c>
       <c r="F259">
-        <v>237</v>
+        <v>170</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8692,13 +8686,13 @@
         <v>536</v>
       </c>
       <c r="B260" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C260" t="s">
         <v>537</v>
       </c>
       <c r="D260" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E260" t="s">
         <v>10</v>
@@ -8712,19 +8706,19 @@
         <v>538</v>
       </c>
       <c r="B261" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C261" t="s">
         <v>539</v>
       </c>
       <c r="D261" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E261" t="s">
         <v>10</v>
       </c>
       <c r="F261">
-        <v>298</v>
+        <v>125</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8732,19 +8726,19 @@
         <v>540</v>
       </c>
       <c r="B262" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C262" t="s">
         <v>541</v>
       </c>
       <c r="D262" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E262" t="s">
         <v>10</v>
       </c>
       <c r="F262">
-        <v>198</v>
+        <v>245</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -8752,19 +8746,19 @@
         <v>542</v>
       </c>
       <c r="B263" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C263" t="s">
         <v>543</v>
       </c>
       <c r="D263" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E263" t="s">
         <v>10</v>
       </c>
       <c r="F263">
-        <v>117</v>
+        <v>246</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -8772,7 +8766,7 @@
         <v>544</v>
       </c>
       <c r="B264" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C264" t="s">
         <v>545</v>
@@ -8784,7 +8778,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>266</v>
+        <v>179</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -8792,7 +8786,7 @@
         <v>546</v>
       </c>
       <c r="B265" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C265" t="s">
         <v>547</v>
@@ -8804,7 +8798,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8812,7 +8806,7 @@
         <v>548</v>
       </c>
       <c r="B266" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C266" t="s">
         <v>549</v>
@@ -8824,7 +8818,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -8832,7 +8826,7 @@
         <v>550</v>
       </c>
       <c r="B267" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C267" t="s">
         <v>551</v>
@@ -8844,7 +8838,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>282</v>
+        <v>193</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -8852,7 +8846,7 @@
         <v>552</v>
       </c>
       <c r="B268" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C268" t="s">
         <v>553</v>
@@ -8864,7 +8858,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>173</v>
+        <v>296</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -8872,7 +8866,7 @@
         <v>554</v>
       </c>
       <c r="B269" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C269" t="s">
         <v>555</v>
@@ -8884,7 +8878,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>117</v>
+        <v>231</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -8892,7 +8886,7 @@
         <v>556</v>
       </c>
       <c r="B270" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C270" t="s">
         <v>557</v>
@@ -8904,7 +8898,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>116</v>
+        <v>196</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -8912,7 +8906,7 @@
         <v>558</v>
       </c>
       <c r="B271" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C271" t="s">
         <v>559</v>
@@ -8924,7 +8918,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>240</v>
+        <v>151</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -8932,7 +8926,7 @@
         <v>560</v>
       </c>
       <c r="B272" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C272" t="s">
         <v>561</v>
@@ -8944,7 +8938,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>134</v>
+        <v>262</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -8952,7 +8946,7 @@
         <v>562</v>
       </c>
       <c r="B273" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C273" t="s">
         <v>563</v>
@@ -8964,7 +8958,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -8972,67 +8966,67 @@
         <v>564</v>
       </c>
       <c r="B274" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="C274" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D274" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E274" t="s">
         <v>10</v>
       </c>
       <c r="F274">
-        <v>107</v>
+        <v>180</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B275" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="C275" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D275" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E275" t="s">
         <v>10</v>
       </c>
       <c r="F275">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B276" t="s">
-        <v>530</v>
+        <v>565</v>
       </c>
       <c r="C276" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D276" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E276" t="s">
         <v>10</v>
       </c>
       <c r="F276">
-        <v>227</v>
+        <v>131</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B277" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C277" t="s">
         <v>572</v>
@@ -9044,7 +9038,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>197</v>
+        <v>139</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9052,7 +9046,7 @@
         <v>573</v>
       </c>
       <c r="B278" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C278" t="s">
         <v>574</v>
@@ -9064,7 +9058,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>177</v>
+        <v>291</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9072,7 +9066,7 @@
         <v>575</v>
       </c>
       <c r="B279" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C279" t="s">
         <v>576</v>
@@ -9084,7 +9078,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>201</v>
+        <v>176</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9092,7 +9086,7 @@
         <v>577</v>
       </c>
       <c r="B280" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C280" t="s">
         <v>578</v>
@@ -9104,7 +9098,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>136</v>
+        <v>207</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9112,7 +9106,7 @@
         <v>579</v>
       </c>
       <c r="B281" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C281" t="s">
         <v>580</v>
@@ -9124,7 +9118,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9132,7 +9126,7 @@
         <v>581</v>
       </c>
       <c r="B282" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C282" t="s">
         <v>582</v>
@@ -9144,7 +9138,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>243</v>
+        <v>100</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9152,7 +9146,7 @@
         <v>583</v>
       </c>
       <c r="B283" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C283" t="s">
         <v>584</v>
@@ -9164,7 +9158,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>241</v>
+        <v>262</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9172,7 +9166,7 @@
         <v>585</v>
       </c>
       <c r="B284" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C284" t="s">
         <v>586</v>
@@ -9184,7 +9178,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>254</v>
+        <v>117</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9192,7 +9186,7 @@
         <v>587</v>
       </c>
       <c r="B285" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C285" t="s">
         <v>588</v>
@@ -9204,7 +9198,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9212,7 +9206,7 @@
         <v>589</v>
       </c>
       <c r="B286" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C286" t="s">
         <v>590</v>
@@ -9224,7 +9218,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>151</v>
+        <v>211</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9232,7 +9226,7 @@
         <v>591</v>
       </c>
       <c r="B287" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C287" t="s">
         <v>592</v>
@@ -9244,7 +9238,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>282</v>
+        <v>162</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9252,7 +9246,7 @@
         <v>593</v>
       </c>
       <c r="B288" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C288" t="s">
         <v>594</v>
@@ -9264,7 +9258,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9272,7 +9266,7 @@
         <v>595</v>
       </c>
       <c r="B289" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C289" t="s">
         <v>596</v>
@@ -9284,7 +9278,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>110</v>
+        <v>297</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9292,7 +9286,7 @@
         <v>597</v>
       </c>
       <c r="B290" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C290" t="s">
         <v>598</v>
@@ -9304,7 +9298,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>127</v>
+        <v>136</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9312,7 +9306,7 @@
         <v>599</v>
       </c>
       <c r="B291" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C291" t="s">
         <v>600</v>
@@ -9324,7 +9318,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>163</v>
+        <v>270</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9332,7 +9326,7 @@
         <v>601</v>
       </c>
       <c r="B292" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C292" t="s">
         <v>602</v>
@@ -9344,7 +9338,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9352,7 +9346,7 @@
         <v>603</v>
       </c>
       <c r="B293" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C293" t="s">
         <v>604</v>
@@ -9364,7 +9358,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>232</v>
+        <v>179</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9372,7 +9366,7 @@
         <v>605</v>
       </c>
       <c r="B294" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C294" t="s">
         <v>606</v>
@@ -9384,7 +9378,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>260</v>
+        <v>173</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9392,7 +9386,7 @@
         <v>607</v>
       </c>
       <c r="B295" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C295" t="s">
         <v>608</v>
@@ -9404,7 +9398,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>135</v>
+        <v>210</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9412,7 +9406,7 @@
         <v>609</v>
       </c>
       <c r="B296" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C296" t="s">
         <v>610</v>
@@ -9424,7 +9418,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>100</v>
+        <v>156</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9432,7 +9426,7 @@
         <v>611</v>
       </c>
       <c r="B297" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C297" t="s">
         <v>612</v>
@@ -9444,7 +9438,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>245</v>
+        <v>229</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9452,7 +9446,7 @@
         <v>613</v>
       </c>
       <c r="B298" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C298" t="s">
         <v>614</v>
@@ -9464,7 +9458,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>107</v>
+        <v>143</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9472,7 +9466,7 @@
         <v>615</v>
       </c>
       <c r="B299" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C299" t="s">
         <v>616</v>
@@ -9484,7 +9478,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>207</v>
+        <v>176</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9492,7 +9486,7 @@
         <v>617</v>
       </c>
       <c r="B300" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C300" t="s">
         <v>618</v>
@@ -9504,7 +9498,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>109</v>
+        <v>280</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9512,7 +9506,7 @@
         <v>619</v>
       </c>
       <c r="B301" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C301" t="s">
         <v>620</v>
@@ -9524,7 +9518,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>250</v>
+        <v>207</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9532,7 +9526,7 @@
         <v>621</v>
       </c>
       <c r="B302" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C302" t="s">
         <v>622</v>
@@ -9544,7 +9538,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9552,7 +9546,7 @@
         <v>623</v>
       </c>
       <c r="B303" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C303" t="s">
         <v>624</v>
@@ -9564,7 +9558,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>144</v>
+        <v>161</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9572,7 +9566,7 @@
         <v>625</v>
       </c>
       <c r="B304" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C304" t="s">
         <v>626</v>
@@ -9584,7 +9578,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>103</v>
+        <v>126</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9592,7 +9586,7 @@
         <v>627</v>
       </c>
       <c r="B305" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C305" t="s">
         <v>628</v>
@@ -9604,7 +9598,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>283</v>
+        <v>228</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9612,7 +9606,7 @@
         <v>629</v>
       </c>
       <c r="B306" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C306" t="s">
         <v>630</v>
@@ -9624,7 +9618,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9632,7 +9626,7 @@
         <v>631</v>
       </c>
       <c r="B307" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C307" t="s">
         <v>632</v>
@@ -9644,7 +9638,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>146</v>
+        <v>223</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9652,7 +9646,7 @@
         <v>633</v>
       </c>
       <c r="B308" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C308" t="s">
         <v>634</v>
@@ -9664,7 +9658,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>255</v>
+        <v>155</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9672,7 +9666,7 @@
         <v>635</v>
       </c>
       <c r="B309" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C309" t="s">
         <v>636</v>
@@ -9684,7 +9678,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>294</v>
+        <v>246</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9692,7 +9686,7 @@
         <v>637</v>
       </c>
       <c r="B310" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C310" t="s">
         <v>638</v>
@@ -9704,7 +9698,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>129</v>
+        <v>166</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9712,7 +9706,7 @@
         <v>639</v>
       </c>
       <c r="B311" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C311" t="s">
         <v>640</v>
@@ -9724,7 +9718,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>228</v>
+        <v>125</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9732,7 +9726,7 @@
         <v>641</v>
       </c>
       <c r="B312" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C312" t="s">
         <v>642</v>
@@ -9744,7 +9738,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>216</v>
+        <v>135</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -9752,7 +9746,7 @@
         <v>643</v>
       </c>
       <c r="B313" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C313" t="s">
         <v>644</v>
@@ -9764,7 +9758,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>217</v>
+        <v>160</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -9772,67 +9766,67 @@
         <v>645</v>
       </c>
       <c r="B314" t="s">
-        <v>571</v>
+        <v>646</v>
       </c>
       <c r="C314" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D314" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E314" t="s">
         <v>10</v>
       </c>
       <c r="F314">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B315" t="s">
-        <v>571</v>
+        <v>646</v>
       </c>
       <c r="C315" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D315" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E315" t="s">
         <v>10</v>
       </c>
       <c r="F315">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B316" t="s">
-        <v>571</v>
+        <v>646</v>
       </c>
       <c r="C316" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D316" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E316" t="s">
         <v>10</v>
       </c>
       <c r="F316">
-        <v>236</v>
+        <v>180</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B317" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C317" t="s">
         <v>653</v>
@@ -9844,7 +9838,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>117</v>
+        <v>216</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -9852,7 +9846,7 @@
         <v>654</v>
       </c>
       <c r="B318" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C318" t="s">
         <v>655</v>
@@ -9864,7 +9858,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>155</v>
+        <v>242</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -9872,7 +9866,7 @@
         <v>656</v>
       </c>
       <c r="B319" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C319" t="s">
         <v>657</v>
@@ -9884,7 +9878,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>193</v>
+        <v>229</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -9892,7 +9886,7 @@
         <v>658</v>
       </c>
       <c r="B320" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C320" t="s">
         <v>659</v>
@@ -9904,7 +9898,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>120</v>
+        <v>213</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -9912,7 +9906,7 @@
         <v>660</v>
       </c>
       <c r="B321" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C321" t="s">
         <v>661</v>
@@ -9924,7 +9918,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -9932,7 +9926,7 @@
         <v>662</v>
       </c>
       <c r="B322" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C322" t="s">
         <v>663</v>
@@ -9944,7 +9938,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>281</v>
+        <v>136</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -9952,7 +9946,7 @@
         <v>664</v>
       </c>
       <c r="B323" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C323" t="s">
         <v>665</v>
@@ -9964,7 +9958,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>162</v>
+        <v>259</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -9972,7 +9966,7 @@
         <v>666</v>
       </c>
       <c r="B324" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C324" t="s">
         <v>667</v>
@@ -9984,7 +9978,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>171</v>
+        <v>184</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -9992,7 +9986,7 @@
         <v>668</v>
       </c>
       <c r="B325" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C325" t="s">
         <v>669</v>
@@ -10004,7 +9998,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>269</v>
+        <v>225</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10012,7 +10006,7 @@
         <v>670</v>
       </c>
       <c r="B326" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C326" t="s">
         <v>671</v>
@@ -10024,7 +10018,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>248</v>
+        <v>180</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10032,7 +10026,7 @@
         <v>672</v>
       </c>
       <c r="B327" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C327" t="s">
         <v>673</v>
@@ -10044,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>174</v>
+        <v>264</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10052,7 +10046,7 @@
         <v>674</v>
       </c>
       <c r="B328" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C328" t="s">
         <v>675</v>
@@ -10064,7 +10058,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>104</v>
+        <v>126</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10072,7 +10066,7 @@
         <v>676</v>
       </c>
       <c r="B329" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C329" t="s">
         <v>677</v>
@@ -10084,7 +10078,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10092,7 +10086,7 @@
         <v>678</v>
       </c>
       <c r="B330" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C330" t="s">
         <v>679</v>
@@ -10104,7 +10098,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>230</v>
+        <v>183</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10112,7 +10106,7 @@
         <v>680</v>
       </c>
       <c r="B331" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C331" t="s">
         <v>681</v>
@@ -10124,7 +10118,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>256</v>
+        <v>146</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10132,7 +10126,7 @@
         <v>682</v>
       </c>
       <c r="B332" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C332" t="s">
         <v>683</v>
@@ -10144,7 +10138,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>104</v>
+        <v>139</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10152,7 +10146,7 @@
         <v>684</v>
       </c>
       <c r="B333" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C333" t="s">
         <v>685</v>
@@ -10164,7 +10158,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>109</v>
+        <v>242</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10172,67 +10166,67 @@
         <v>686</v>
       </c>
       <c r="B334" t="s">
-        <v>652</v>
+        <v>687</v>
       </c>
       <c r="C334" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D334" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E334" t="s">
         <v>10</v>
       </c>
       <c r="F334">
-        <v>277</v>
+        <v>299</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B335" t="s">
-        <v>652</v>
+        <v>687</v>
       </c>
       <c r="C335" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D335" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E335" t="s">
         <v>10</v>
       </c>
       <c r="F335">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B336" t="s">
-        <v>652</v>
+        <v>687</v>
       </c>
       <c r="C336" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D336" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E336" t="s">
         <v>10</v>
       </c>
       <c r="F336">
-        <v>244</v>
+        <v>125</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B337" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C337" t="s">
         <v>694</v>
@@ -10244,7 +10238,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>242</v>
+        <v>142</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10252,7 +10246,7 @@
         <v>695</v>
       </c>
       <c r="B338" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C338" t="s">
         <v>696</v>
@@ -10264,7 +10258,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>260</v>
+        <v>283</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10272,7 +10266,7 @@
         <v>697</v>
       </c>
       <c r="B339" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C339" t="s">
         <v>698</v>
@@ -10284,7 +10278,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>261</v>
+        <v>133</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10292,7 +10286,7 @@
         <v>699</v>
       </c>
       <c r="B340" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C340" t="s">
         <v>700</v>
@@ -10304,7 +10298,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10312,7 +10306,7 @@
         <v>701</v>
       </c>
       <c r="B341" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C341" t="s">
         <v>702</v>
@@ -10324,7 +10318,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10332,7 +10326,7 @@
         <v>703</v>
       </c>
       <c r="B342" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C342" t="s">
         <v>704</v>
@@ -10344,7 +10338,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>141</v>
+        <v>185</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10352,7 +10346,7 @@
         <v>705</v>
       </c>
       <c r="B343" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C343" t="s">
         <v>706</v>
@@ -10364,7 +10358,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>203</v>
+        <v>264</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10372,7 +10366,7 @@
         <v>707</v>
       </c>
       <c r="B344" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C344" t="s">
         <v>708</v>
@@ -10384,7 +10378,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>178</v>
+        <v>105</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10392,7 +10386,7 @@
         <v>709</v>
       </c>
       <c r="B345" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C345" t="s">
         <v>710</v>
@@ -10404,7 +10398,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>122</v>
+        <v>213</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10412,7 +10406,7 @@
         <v>711</v>
       </c>
       <c r="B346" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C346" t="s">
         <v>712</v>
@@ -10424,7 +10418,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10432,7 +10426,7 @@
         <v>713</v>
       </c>
       <c r="B347" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C347" t="s">
         <v>714</v>
@@ -10444,7 +10438,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>218</v>
+        <v>270</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10452,7 +10446,7 @@
         <v>715</v>
       </c>
       <c r="B348" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C348" t="s">
         <v>716</v>
@@ -10464,7 +10458,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>299</v>
+        <v>120</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -10472,7 +10466,7 @@
         <v>717</v>
       </c>
       <c r="B349" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C349" t="s">
         <v>718</v>
@@ -10484,7 +10478,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>135</v>
+        <v>261</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10492,7 +10486,7 @@
         <v>719</v>
       </c>
       <c r="B350" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C350" t="s">
         <v>720</v>
@@ -10504,7 +10498,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10512,7 +10506,7 @@
         <v>721</v>
       </c>
       <c r="B351" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C351" t="s">
         <v>722</v>
@@ -10524,7 +10518,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>123</v>
+        <v>202</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10532,7 +10526,7 @@
         <v>723</v>
       </c>
       <c r="B352" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C352" t="s">
         <v>724</v>
@@ -10544,7 +10538,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>151</v>
+        <v>188</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10552,7 +10546,7 @@
         <v>725</v>
       </c>
       <c r="B353" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C353" t="s">
         <v>726</v>
@@ -10564,7 +10558,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>220</v>
+        <v>142</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -10572,67 +10566,67 @@
         <v>727</v>
       </c>
       <c r="B354" t="s">
-        <v>693</v>
+        <v>728</v>
       </c>
       <c r="C354" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D354" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E354" t="s">
         <v>10</v>
       </c>
       <c r="F354">
-        <v>229</v>
+        <v>120</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B355" t="s">
-        <v>693</v>
+        <v>728</v>
       </c>
       <c r="C355" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D355" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E355" t="s">
         <v>10</v>
       </c>
       <c r="F355">
-        <v>273</v>
+        <v>166</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B356" t="s">
-        <v>693</v>
+        <v>728</v>
       </c>
       <c r="C356" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D356" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E356" t="s">
         <v>10</v>
       </c>
       <c r="F356">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B357" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C357" t="s">
         <v>735</v>
@@ -10644,7 +10638,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>100</v>
+        <v>156</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10652,7 +10646,7 @@
         <v>736</v>
       </c>
       <c r="B358" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C358" t="s">
         <v>737</v>
@@ -10664,7 +10658,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>253</v>
+        <v>102</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10672,7 +10666,7 @@
         <v>738</v>
       </c>
       <c r="B359" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C359" t="s">
         <v>739</v>
@@ -10684,7 +10678,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>195</v>
+        <v>296</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10692,7 +10686,7 @@
         <v>740</v>
       </c>
       <c r="B360" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C360" t="s">
         <v>741</v>
@@ -10704,7 +10698,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10712,7 +10706,7 @@
         <v>742</v>
       </c>
       <c r="B361" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C361" t="s">
         <v>743</v>
@@ -10724,7 +10718,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10732,7 +10726,7 @@
         <v>744</v>
       </c>
       <c r="B362" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C362" t="s">
         <v>745</v>
@@ -10744,7 +10738,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>277</v>
+        <v>108</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -10752,7 +10746,7 @@
         <v>746</v>
       </c>
       <c r="B363" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C363" t="s">
         <v>747</v>
@@ -10764,7 +10758,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -10772,7 +10766,7 @@
         <v>748</v>
       </c>
       <c r="B364" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C364" t="s">
         <v>749</v>
@@ -10784,7 +10778,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -10792,7 +10786,7 @@
         <v>750</v>
       </c>
       <c r="B365" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C365" t="s">
         <v>751</v>
@@ -10804,7 +10798,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>214</v>
+        <v>160</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -10812,7 +10806,7 @@
         <v>752</v>
       </c>
       <c r="B366" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C366" t="s">
         <v>753</v>
@@ -10824,7 +10818,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>194</v>
+        <v>103</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -10832,7 +10826,7 @@
         <v>754</v>
       </c>
       <c r="B367" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C367" t="s">
         <v>755</v>
@@ -10844,7 +10838,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>279</v>
+        <v>211</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -10852,7 +10846,7 @@
         <v>756</v>
       </c>
       <c r="B368" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C368" t="s">
         <v>757</v>
@@ -10864,7 +10858,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>268</v>
+        <v>179</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -10872,7 +10866,7 @@
         <v>758</v>
       </c>
       <c r="B369" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C369" t="s">
         <v>759</v>
@@ -10884,7 +10878,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>156</v>
+        <v>108</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -10892,19 +10886,19 @@
         <v>760</v>
       </c>
       <c r="B370" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C370" t="s">
         <v>761</v>
       </c>
       <c r="D370" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E370" t="s">
         <v>10</v>
       </c>
       <c r="F370">
-        <v>145</v>
+        <v>291</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -10912,19 +10906,19 @@
         <v>762</v>
       </c>
       <c r="B371" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C371" t="s">
         <v>763</v>
       </c>
       <c r="D371" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E371" t="s">
         <v>10</v>
       </c>
       <c r="F371">
-        <v>282</v>
+        <v>244</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -10932,19 +10926,19 @@
         <v>764</v>
       </c>
       <c r="B372" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C372" t="s">
         <v>765</v>
       </c>
       <c r="D372" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E372" t="s">
         <v>10</v>
       </c>
       <c r="F372">
-        <v>105</v>
+        <v>141</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -10952,19 +10946,19 @@
         <v>766</v>
       </c>
       <c r="B373" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="C373" t="s">
         <v>767</v>
       </c>
       <c r="D373" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E373" t="s">
         <v>10</v>
       </c>
       <c r="F373">
-        <v>254</v>
+        <v>176</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -10972,10 +10966,10 @@
         <v>768</v>
       </c>
       <c r="B374" t="s">
-        <v>734</v>
+        <v>769</v>
       </c>
       <c r="C374" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D374" t="s">
         <v>9</v>
@@ -10984,18 +10978,18 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>284</v>
+        <v>232</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B375" t="s">
-        <v>734</v>
+        <v>769</v>
       </c>
       <c r="C375" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D375" t="s">
         <v>13</v>
@@ -11004,27 +10998,27 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>167</v>
+        <v>217</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B376" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C376" t="s">
         <v>774</v>
       </c>
       <c r="D376" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E376" t="s">
         <v>10</v>
       </c>
       <c r="F376">
-        <v>237</v>
+        <v>187</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11032,19 +11026,19 @@
         <v>775</v>
       </c>
       <c r="B377" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C377" t="s">
         <v>776</v>
       </c>
       <c r="D377" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E377" t="s">
         <v>10</v>
       </c>
       <c r="F377">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11052,19 +11046,19 @@
         <v>777</v>
       </c>
       <c r="B378" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C378" t="s">
         <v>778</v>
       </c>
       <c r="D378" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E378" t="s">
         <v>10</v>
       </c>
       <c r="F378">
-        <v>234</v>
+        <v>176</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11072,19 +11066,19 @@
         <v>779</v>
       </c>
       <c r="B379" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C379" t="s">
         <v>780</v>
       </c>
       <c r="D379" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E379" t="s">
         <v>10</v>
       </c>
       <c r="F379">
-        <v>162</v>
+        <v>190</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11092,19 +11086,19 @@
         <v>781</v>
       </c>
       <c r="B380" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C380" t="s">
         <v>782</v>
       </c>
       <c r="D380" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E380" t="s">
         <v>10</v>
       </c>
       <c r="F380">
-        <v>155</v>
+        <v>243</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11112,19 +11106,19 @@
         <v>783</v>
       </c>
       <c r="B381" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C381" t="s">
         <v>784</v>
       </c>
       <c r="D381" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E381" t="s">
         <v>10</v>
       </c>
       <c r="F381">
-        <v>169</v>
+        <v>112</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11132,19 +11126,19 @@
         <v>785</v>
       </c>
       <c r="B382" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C382" t="s">
         <v>786</v>
       </c>
       <c r="D382" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E382" t="s">
         <v>10</v>
       </c>
       <c r="F382">
-        <v>159</v>
+        <v>299</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11152,19 +11146,19 @@
         <v>787</v>
       </c>
       <c r="B383" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C383" t="s">
         <v>788</v>
       </c>
       <c r="D383" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E383" t="s">
         <v>10</v>
       </c>
       <c r="F383">
-        <v>259</v>
+        <v>177</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11172,19 +11166,19 @@
         <v>789</v>
       </c>
       <c r="B384" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C384" t="s">
         <v>790</v>
       </c>
       <c r="D384" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E384" t="s">
         <v>10</v>
       </c>
       <c r="F384">
-        <v>291</v>
+        <v>115</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11192,19 +11186,19 @@
         <v>791</v>
       </c>
       <c r="B385" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C385" t="s">
         <v>792</v>
       </c>
       <c r="D385" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E385" t="s">
         <v>10</v>
       </c>
       <c r="F385">
-        <v>264</v>
+        <v>144</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11212,19 +11206,19 @@
         <v>793</v>
       </c>
       <c r="B386" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C386" t="s">
         <v>794</v>
       </c>
       <c r="D386" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E386" t="s">
         <v>10</v>
       </c>
       <c r="F386">
-        <v>114</v>
+        <v>222</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11232,19 +11226,19 @@
         <v>795</v>
       </c>
       <c r="B387" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C387" t="s">
         <v>796</v>
       </c>
       <c r="D387" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E387" t="s">
         <v>10</v>
       </c>
       <c r="F387">
-        <v>132</v>
+        <v>195</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -11252,19 +11246,19 @@
         <v>797</v>
       </c>
       <c r="B388" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C388" t="s">
         <v>798</v>
       </c>
       <c r="D388" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E388" t="s">
         <v>10</v>
       </c>
       <c r="F388">
-        <v>264</v>
+        <v>164</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11272,19 +11266,19 @@
         <v>799</v>
       </c>
       <c r="B389" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C389" t="s">
         <v>800</v>
       </c>
       <c r="D389" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E389" t="s">
         <v>10</v>
       </c>
       <c r="F389">
-        <v>128</v>
+        <v>296</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11292,19 +11286,19 @@
         <v>801</v>
       </c>
       <c r="B390" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C390" t="s">
         <v>802</v>
       </c>
       <c r="D390" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E390" t="s">
         <v>10</v>
       </c>
       <c r="F390">
-        <v>127</v>
+        <v>190</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11312,19 +11306,19 @@
         <v>803</v>
       </c>
       <c r="B391" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C391" t="s">
         <v>804</v>
       </c>
       <c r="D391" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E391" t="s">
         <v>10</v>
       </c>
       <c r="F391">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11332,19 +11326,19 @@
         <v>805</v>
       </c>
       <c r="B392" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C392" t="s">
         <v>806</v>
       </c>
       <c r="D392" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E392" t="s">
         <v>10</v>
       </c>
       <c r="F392">
-        <v>267</v>
+        <v>213</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -11352,19 +11346,19 @@
         <v>807</v>
       </c>
       <c r="B393" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C393" t="s">
         <v>808</v>
       </c>
       <c r="D393" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E393" t="s">
         <v>10</v>
       </c>
       <c r="F393">
-        <v>173</v>
+        <v>262</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -11372,10 +11366,10 @@
         <v>809</v>
       </c>
       <c r="B394" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="C394" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D394" t="s">
         <v>9</v>
@@ -11384,18 +11378,18 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B395" t="s">
-        <v>773</v>
+        <v>810</v>
       </c>
       <c r="C395" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D395" t="s">
         <v>13</v>
@@ -11404,27 +11398,27 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>162</v>
+        <v>236</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B396" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C396" t="s">
         <v>815</v>
       </c>
       <c r="D396" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E396" t="s">
         <v>10</v>
       </c>
       <c r="F396">
-        <v>187</v>
+        <v>255</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11432,19 +11426,19 @@
         <v>816</v>
       </c>
       <c r="B397" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C397" t="s">
         <v>817</v>
       </c>
       <c r="D397" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E397" t="s">
         <v>10</v>
       </c>
       <c r="F397">
-        <v>162</v>
+        <v>107</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -11452,19 +11446,19 @@
         <v>818</v>
       </c>
       <c r="B398" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C398" t="s">
         <v>819</v>
       </c>
       <c r="D398" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E398" t="s">
         <v>10</v>
       </c>
       <c r="F398">
-        <v>106</v>
+        <v>121</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11472,19 +11466,19 @@
         <v>820</v>
       </c>
       <c r="B399" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C399" t="s">
         <v>821</v>
       </c>
       <c r="D399" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E399" t="s">
         <v>10</v>
       </c>
       <c r="F399">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11492,19 +11486,19 @@
         <v>822</v>
       </c>
       <c r="B400" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C400" t="s">
         <v>823</v>
       </c>
       <c r="D400" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E400" t="s">
         <v>10</v>
       </c>
       <c r="F400">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11512,19 +11506,19 @@
         <v>824</v>
       </c>
       <c r="B401" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C401" t="s">
         <v>825</v>
       </c>
       <c r="D401" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E401" t="s">
         <v>10</v>
       </c>
       <c r="F401">
-        <v>289</v>
+        <v>227</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11532,19 +11526,19 @@
         <v>826</v>
       </c>
       <c r="B402" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C402" t="s">
         <v>827</v>
       </c>
       <c r="D402" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E402" t="s">
         <v>10</v>
       </c>
       <c r="F402">
-        <v>240</v>
+        <v>127</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -11552,19 +11546,19 @@
         <v>828</v>
       </c>
       <c r="B403" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C403" t="s">
         <v>829</v>
       </c>
       <c r="D403" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E403" t="s">
         <v>10</v>
       </c>
       <c r="F403">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -11572,59 +11566,59 @@
         <v>830</v>
       </c>
       <c r="B404" t="s">
-        <v>814</v>
+        <v>831</v>
       </c>
       <c r="C404" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D404" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E404" t="s">
         <v>10</v>
       </c>
       <c r="F404">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B405" t="s">
-        <v>814</v>
+        <v>831</v>
       </c>
       <c r="C405" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D405" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E405" t="s">
         <v>10</v>
       </c>
       <c r="F405">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B406" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C406" t="s">
         <v>836</v>
       </c>
       <c r="D406" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E406" t="s">
         <v>10</v>
       </c>
       <c r="F406">
-        <v>125</v>
+        <v>235</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11632,19 +11626,19 @@
         <v>837</v>
       </c>
       <c r="B407" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C407" t="s">
         <v>838</v>
       </c>
       <c r="D407" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E407" t="s">
         <v>10</v>
       </c>
       <c r="F407">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11652,19 +11646,19 @@
         <v>839</v>
       </c>
       <c r="B408" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C408" t="s">
         <v>840</v>
       </c>
       <c r="D408" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E408" t="s">
         <v>10</v>
       </c>
       <c r="F408">
-        <v>247</v>
+        <v>222</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11672,19 +11666,19 @@
         <v>841</v>
       </c>
       <c r="B409" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C409" t="s">
         <v>842</v>
       </c>
       <c r="D409" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E409" t="s">
         <v>10</v>
       </c>
       <c r="F409">
-        <v>253</v>
+        <v>235</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11692,19 +11686,19 @@
         <v>843</v>
       </c>
       <c r="B410" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C410" t="s">
         <v>844</v>
       </c>
       <c r="D410" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E410" t="s">
         <v>10</v>
       </c>
       <c r="F410">
-        <v>270</v>
+        <v>291</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11712,19 +11706,19 @@
         <v>845</v>
       </c>
       <c r="B411" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C411" t="s">
         <v>846</v>
       </c>
       <c r="D411" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E411" t="s">
         <v>10</v>
       </c>
       <c r="F411">
-        <v>240</v>
+        <v>202</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11732,19 +11726,19 @@
         <v>847</v>
       </c>
       <c r="B412" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C412" t="s">
         <v>848</v>
       </c>
       <c r="D412" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E412" t="s">
         <v>10</v>
       </c>
       <c r="F412">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -11752,19 +11746,19 @@
         <v>849</v>
       </c>
       <c r="B413" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C413" t="s">
         <v>850</v>
       </c>
       <c r="D413" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E413" t="s">
         <v>10</v>
       </c>
       <c r="F413">
-        <v>161</v>
+        <v>246</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -11772,19 +11766,19 @@
         <v>851</v>
       </c>
       <c r="B414" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C414" t="s">
         <v>852</v>
       </c>
       <c r="D414" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E414" t="s">
         <v>10</v>
       </c>
       <c r="F414">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -11792,19 +11786,19 @@
         <v>853</v>
       </c>
       <c r="B415" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C415" t="s">
         <v>854</v>
       </c>
       <c r="D415" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E415" t="s">
         <v>10</v>
       </c>
       <c r="F415">
-        <v>171</v>
+        <v>112</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -11812,19 +11806,19 @@
         <v>855</v>
       </c>
       <c r="B416" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C416" t="s">
         <v>856</v>
       </c>
       <c r="D416" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E416" t="s">
         <v>10</v>
       </c>
       <c r="F416">
-        <v>157</v>
+        <v>284</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -11832,19 +11826,19 @@
         <v>857</v>
       </c>
       <c r="B417" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C417" t="s">
         <v>858</v>
       </c>
       <c r="D417" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E417" t="s">
         <v>10</v>
       </c>
       <c r="F417">
-        <v>222</v>
+        <v>257</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -11852,19 +11846,19 @@
         <v>859</v>
       </c>
       <c r="B418" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C418" t="s">
         <v>860</v>
       </c>
       <c r="D418" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E418" t="s">
         <v>10</v>
       </c>
       <c r="F418">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -11872,19 +11866,19 @@
         <v>861</v>
       </c>
       <c r="B419" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C419" t="s">
         <v>862</v>
       </c>
       <c r="D419" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E419" t="s">
         <v>10</v>
       </c>
       <c r="F419">
-        <v>214</v>
+        <v>289</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -11892,13 +11886,13 @@
         <v>863</v>
       </c>
       <c r="B420" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C420" t="s">
         <v>864</v>
       </c>
       <c r="D420" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E420" t="s">
         <v>10</v>
@@ -11912,19 +11906,19 @@
         <v>865</v>
       </c>
       <c r="B421" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C421" t="s">
         <v>866</v>
       </c>
       <c r="D421" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E421" t="s">
         <v>10</v>
       </c>
       <c r="F421">
-        <v>175</v>
+        <v>265</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -11932,19 +11926,19 @@
         <v>867</v>
       </c>
       <c r="B422" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C422" t="s">
         <v>868</v>
       </c>
       <c r="D422" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E422" t="s">
         <v>10</v>
       </c>
       <c r="F422">
-        <v>248</v>
+        <v>117</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -11952,47 +11946,47 @@
         <v>869</v>
       </c>
       <c r="B423" t="s">
-        <v>835</v>
+        <v>870</v>
       </c>
       <c r="C423" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D423" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E423" t="s">
         <v>10</v>
       </c>
       <c r="F423">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B424" t="s">
-        <v>835</v>
+        <v>870</v>
       </c>
       <c r="C424" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D424" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E424" t="s">
         <v>10</v>
       </c>
       <c r="F424">
-        <v>223</v>
+        <v>132</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B425" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C425" t="s">
         <v>875</v>
@@ -12004,7 +11998,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>147</v>
+        <v>231</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -12012,7 +12006,7 @@
         <v>876</v>
       </c>
       <c r="B426" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C426" t="s">
         <v>877</v>
@@ -12024,7 +12018,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>229</v>
+        <v>140</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12032,7 +12026,7 @@
         <v>878</v>
       </c>
       <c r="B427" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C427" t="s">
         <v>879</v>
@@ -12044,7 +12038,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>230</v>
+        <v>247</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12052,7 +12046,7 @@
         <v>880</v>
       </c>
       <c r="B428" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C428" t="s">
         <v>881</v>
@@ -12064,7 +12058,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>253</v>
+        <v>177</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12072,7 +12066,7 @@
         <v>882</v>
       </c>
       <c r="B429" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C429" t="s">
         <v>883</v>
@@ -12084,7 +12078,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>181</v>
+        <v>120</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12092,7 +12086,7 @@
         <v>884</v>
       </c>
       <c r="B430" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C430" t="s">
         <v>885</v>
@@ -12104,7 +12098,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>102</v>
+        <v>237</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12112,7 +12106,7 @@
         <v>886</v>
       </c>
       <c r="B431" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C431" t="s">
         <v>887</v>
@@ -12124,7 +12118,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>107</v>
+        <v>195</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12132,67 +12126,67 @@
         <v>888</v>
       </c>
       <c r="B432" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="C432" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D432" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E432" t="s">
         <v>10</v>
       </c>
       <c r="F432">
-        <v>189</v>
+        <v>222</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B433" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="C433" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D433" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E433" t="s">
         <v>10</v>
       </c>
       <c r="F433">
-        <v>191</v>
+        <v>158</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B434" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="C434" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D434" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E434" t="s">
         <v>10</v>
       </c>
       <c r="F434">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B435" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C435" t="s">
         <v>896</v>
@@ -12204,7 +12198,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>132</v>
+        <v>195</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12212,7 +12206,7 @@
         <v>897</v>
       </c>
       <c r="B436" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C436" t="s">
         <v>898</v>
@@ -12224,7 +12218,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>172</v>
+        <v>209</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12232,7 +12226,7 @@
         <v>899</v>
       </c>
       <c r="B437" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C437" t="s">
         <v>900</v>
@@ -12244,7 +12238,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>140</v>
+        <v>278</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12252,7 +12246,7 @@
         <v>901</v>
       </c>
       <c r="B438" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C438" t="s">
         <v>902</v>
@@ -12264,7 +12258,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12272,7 +12266,7 @@
         <v>903</v>
       </c>
       <c r="B439" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C439" t="s">
         <v>904</v>
@@ -12284,7 +12278,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>105</v>
+        <v>193</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12292,7 +12286,7 @@
         <v>905</v>
       </c>
       <c r="B440" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C440" t="s">
         <v>906</v>
@@ -12304,7 +12298,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>274</v>
+        <v>168</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12312,7 +12306,7 @@
         <v>907</v>
       </c>
       <c r="B441" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C441" t="s">
         <v>908</v>
@@ -12324,7 +12318,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12332,7 +12326,7 @@
         <v>909</v>
       </c>
       <c r="B442" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C442" t="s">
         <v>910</v>
@@ -12344,7 +12338,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12352,7 +12346,7 @@
         <v>911</v>
       </c>
       <c r="B443" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C443" t="s">
         <v>912</v>
@@ -12364,7 +12358,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>288</v>
+        <v>103</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12372,7 +12366,7 @@
         <v>913</v>
       </c>
       <c r="B444" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C444" t="s">
         <v>914</v>
@@ -12384,7 +12378,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>120</v>
+        <v>166</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12392,7 +12386,7 @@
         <v>915</v>
       </c>
       <c r="B445" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C445" t="s">
         <v>916</v>
@@ -12404,7 +12398,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>120</v>
+        <v>252</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12412,7 +12406,7 @@
         <v>917</v>
       </c>
       <c r="B446" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C446" t="s">
         <v>918</v>
@@ -12424,7 +12418,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>192</v>
+        <v>149</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12432,7 +12426,7 @@
         <v>919</v>
       </c>
       <c r="B447" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C447" t="s">
         <v>920</v>
@@ -12444,7 +12438,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>289</v>
+        <v>201</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12452,19 +12446,19 @@
         <v>921</v>
       </c>
       <c r="B448" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C448" t="s">
         <v>922</v>
       </c>
       <c r="D448" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E448" t="s">
         <v>10</v>
       </c>
       <c r="F448">
-        <v>217</v>
+        <v>174</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12472,19 +12466,19 @@
         <v>923</v>
       </c>
       <c r="B449" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C449" t="s">
         <v>924</v>
       </c>
       <c r="D449" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E449" t="s">
         <v>10</v>
       </c>
       <c r="F449">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -12492,19 +12486,19 @@
         <v>925</v>
       </c>
       <c r="B450" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C450" t="s">
         <v>926</v>
       </c>
       <c r="D450" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E450" t="s">
         <v>10</v>
       </c>
       <c r="F450">
-        <v>108</v>
+        <v>271</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12512,19 +12506,19 @@
         <v>927</v>
       </c>
       <c r="B451" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="C451" t="s">
         <v>928</v>
       </c>
       <c r="D451" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E451" t="s">
         <v>10</v>
       </c>
       <c r="F451">
-        <v>215</v>
+        <v>178</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12532,10 +12526,10 @@
         <v>929</v>
       </c>
       <c r="B452" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="C452" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D452" t="s">
         <v>9</v>
@@ -12544,18 +12538,18 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>189</v>
+        <v>156</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B453" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="C453" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D453" t="s">
         <v>13</v>
@@ -12564,27 +12558,27 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>236</v>
+        <v>223</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B454" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C454" t="s">
         <v>935</v>
       </c>
       <c r="D454" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E454" t="s">
         <v>10</v>
       </c>
       <c r="F454">
-        <v>280</v>
+        <v>107</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -12592,19 +12586,19 @@
         <v>936</v>
       </c>
       <c r="B455" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C455" t="s">
         <v>937</v>
       </c>
       <c r="D455" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E455" t="s">
         <v>10</v>
       </c>
       <c r="F455">
-        <v>293</v>
+        <v>124</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12612,19 +12606,19 @@
         <v>938</v>
       </c>
       <c r="B456" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C456" t="s">
         <v>939</v>
       </c>
       <c r="D456" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E456" t="s">
         <v>10</v>
       </c>
       <c r="F456">
-        <v>108</v>
+        <v>169</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12632,19 +12626,19 @@
         <v>940</v>
       </c>
       <c r="B457" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C457" t="s">
         <v>941</v>
       </c>
       <c r="D457" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E457" t="s">
         <v>10</v>
       </c>
       <c r="F457">
-        <v>262</v>
+        <v>284</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12652,19 +12646,19 @@
         <v>942</v>
       </c>
       <c r="B458" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C458" t="s">
         <v>943</v>
       </c>
       <c r="D458" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E458" t="s">
         <v>10</v>
       </c>
       <c r="F458">
-        <v>104</v>
+        <v>176</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12672,19 +12666,19 @@
         <v>944</v>
       </c>
       <c r="B459" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C459" t="s">
         <v>945</v>
       </c>
       <c r="D459" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E459" t="s">
         <v>10</v>
       </c>
       <c r="F459">
-        <v>270</v>
+        <v>137</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12692,19 +12686,19 @@
         <v>946</v>
       </c>
       <c r="B460" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C460" t="s">
         <v>947</v>
       </c>
       <c r="D460" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E460" t="s">
         <v>10</v>
       </c>
       <c r="F460">
-        <v>111</v>
+        <v>242</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12712,19 +12706,19 @@
         <v>948</v>
       </c>
       <c r="B461" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C461" t="s">
         <v>949</v>
       </c>
       <c r="D461" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E461" t="s">
         <v>10</v>
       </c>
       <c r="F461">
-        <v>140</v>
+        <v>192</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12732,19 +12726,19 @@
         <v>950</v>
       </c>
       <c r="B462" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C462" t="s">
         <v>951</v>
       </c>
       <c r="D462" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E462" t="s">
         <v>10</v>
       </c>
       <c r="F462">
-        <v>287</v>
+        <v>183</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -12752,19 +12746,19 @@
         <v>952</v>
       </c>
       <c r="B463" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C463" t="s">
         <v>953</v>
       </c>
       <c r="D463" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E463" t="s">
         <v>10</v>
       </c>
       <c r="F463">
-        <v>161</v>
+        <v>125</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -12772,19 +12766,19 @@
         <v>954</v>
       </c>
       <c r="B464" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C464" t="s">
         <v>955</v>
       </c>
       <c r="D464" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E464" t="s">
         <v>10</v>
       </c>
       <c r="F464">
-        <v>246</v>
+        <v>174</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -12792,19 +12786,19 @@
         <v>956</v>
       </c>
       <c r="B465" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C465" t="s">
         <v>957</v>
       </c>
       <c r="D465" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E465" t="s">
         <v>10</v>
       </c>
       <c r="F465">
-        <v>169</v>
+        <v>299</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -12812,19 +12806,19 @@
         <v>958</v>
       </c>
       <c r="B466" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C466" t="s">
         <v>959</v>
       </c>
       <c r="D466" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E466" t="s">
         <v>10</v>
       </c>
       <c r="F466">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -12832,19 +12826,19 @@
         <v>960</v>
       </c>
       <c r="B467" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C467" t="s">
         <v>961</v>
       </c>
       <c r="D467" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E467" t="s">
         <v>10</v>
       </c>
       <c r="F467">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -12852,19 +12846,19 @@
         <v>962</v>
       </c>
       <c r="B468" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C468" t="s">
         <v>963</v>
       </c>
       <c r="D468" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E468" t="s">
         <v>10</v>
       </c>
       <c r="F468">
-        <v>289</v>
+        <v>127</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -12872,19 +12866,19 @@
         <v>964</v>
       </c>
       <c r="B469" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C469" t="s">
         <v>965</v>
       </c>
       <c r="D469" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E469" t="s">
         <v>10</v>
       </c>
       <c r="F469">
-        <v>246</v>
+        <v>106</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -12892,19 +12886,19 @@
         <v>966</v>
       </c>
       <c r="B470" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C470" t="s">
         <v>967</v>
       </c>
       <c r="D470" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E470" t="s">
         <v>10</v>
       </c>
       <c r="F470">
-        <v>159</v>
+        <v>248</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -12912,19 +12906,19 @@
         <v>968</v>
       </c>
       <c r="B471" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C471" t="s">
         <v>969</v>
       </c>
       <c r="D471" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E471" t="s">
         <v>10</v>
       </c>
       <c r="F471">
-        <v>150</v>
+        <v>258</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -12932,19 +12926,19 @@
         <v>970</v>
       </c>
       <c r="B472" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C472" t="s">
         <v>971</v>
       </c>
       <c r="D472" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E472" t="s">
         <v>10</v>
       </c>
       <c r="F472">
-        <v>283</v>
+        <v>176</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -12952,19 +12946,19 @@
         <v>972</v>
       </c>
       <c r="B473" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C473" t="s">
         <v>973</v>
       </c>
       <c r="D473" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E473" t="s">
         <v>10</v>
       </c>
       <c r="F473">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -12972,19 +12966,19 @@
         <v>974</v>
       </c>
       <c r="B474" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C474" t="s">
         <v>975</v>
       </c>
       <c r="D474" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E474" t="s">
         <v>10</v>
       </c>
       <c r="F474">
-        <v>147</v>
+        <v>186</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -12992,19 +12986,19 @@
         <v>976</v>
       </c>
       <c r="B475" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C475" t="s">
         <v>977</v>
       </c>
       <c r="D475" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E475" t="s">
         <v>10</v>
       </c>
       <c r="F475">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -13012,19 +13006,19 @@
         <v>978</v>
       </c>
       <c r="B476" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C476" t="s">
         <v>979</v>
       </c>
       <c r="D476" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E476" t="s">
         <v>10</v>
       </c>
       <c r="F476">
-        <v>144</v>
+        <v>240</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13032,19 +13026,19 @@
         <v>980</v>
       </c>
       <c r="B477" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C477" t="s">
         <v>981</v>
       </c>
       <c r="D477" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E477" t="s">
         <v>10</v>
       </c>
       <c r="F477">
-        <v>102</v>
+        <v>261</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13052,19 +13046,19 @@
         <v>982</v>
       </c>
       <c r="B478" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C478" t="s">
         <v>983</v>
       </c>
       <c r="D478" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E478" t="s">
         <v>10</v>
       </c>
       <c r="F478">
-        <v>292</v>
+        <v>182</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13072,19 +13066,19 @@
         <v>984</v>
       </c>
       <c r="B479" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C479" t="s">
         <v>985</v>
       </c>
       <c r="D479" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E479" t="s">
         <v>10</v>
       </c>
       <c r="F479">
-        <v>192</v>
+        <v>278</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -13092,19 +13086,19 @@
         <v>986</v>
       </c>
       <c r="B480" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C480" t="s">
         <v>987</v>
       </c>
       <c r="D480" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E480" t="s">
         <v>10</v>
       </c>
       <c r="F480">
-        <v>287</v>
+        <v>199</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13112,19 +13106,19 @@
         <v>988</v>
       </c>
       <c r="B481" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C481" t="s">
         <v>989</v>
       </c>
       <c r="D481" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E481" t="s">
         <v>10</v>
       </c>
       <c r="F481">
-        <v>290</v>
+        <v>189</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13132,19 +13126,19 @@
         <v>990</v>
       </c>
       <c r="B482" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C482" t="s">
         <v>991</v>
       </c>
       <c r="D482" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E482" t="s">
         <v>10</v>
       </c>
       <c r="F482">
-        <v>115</v>
+        <v>248</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13152,19 +13146,19 @@
         <v>992</v>
       </c>
       <c r="B483" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C483" t="s">
         <v>993</v>
       </c>
       <c r="D483" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E483" t="s">
         <v>10</v>
       </c>
       <c r="F483">
-        <v>233</v>
+        <v>183</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13172,19 +13166,19 @@
         <v>994</v>
       </c>
       <c r="B484" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C484" t="s">
         <v>995</v>
       </c>
       <c r="D484" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E484" t="s">
         <v>10</v>
       </c>
       <c r="F484">
-        <v>173</v>
+        <v>255</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13192,19 +13186,19 @@
         <v>996</v>
       </c>
       <c r="B485" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C485" t="s">
         <v>997</v>
       </c>
       <c r="D485" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E485" t="s">
         <v>10</v>
       </c>
       <c r="F485">
-        <v>269</v>
+        <v>295</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13212,19 +13206,19 @@
         <v>998</v>
       </c>
       <c r="B486" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C486" t="s">
         <v>999</v>
       </c>
       <c r="D486" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E486" t="s">
         <v>10</v>
       </c>
       <c r="F486">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13232,19 +13226,19 @@
         <v>1000</v>
       </c>
       <c r="B487" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C487" t="s">
         <v>1001</v>
       </c>
       <c r="D487" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E487" t="s">
         <v>10</v>
       </c>
       <c r="F487">
-        <v>261</v>
+        <v>246</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13252,19 +13246,19 @@
         <v>1002</v>
       </c>
       <c r="B488" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C488" t="s">
         <v>1003</v>
       </c>
       <c r="D488" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E488" t="s">
         <v>10</v>
       </c>
       <c r="F488">
-        <v>177</v>
+        <v>298</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13272,19 +13266,19 @@
         <v>1004</v>
       </c>
       <c r="B489" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C489" t="s">
         <v>1005</v>
       </c>
       <c r="D489" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E489" t="s">
         <v>10</v>
       </c>
       <c r="F489">
-        <v>141</v>
+        <v>171</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13292,19 +13286,19 @@
         <v>1006</v>
       </c>
       <c r="B490" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C490" t="s">
         <v>1007</v>
       </c>
       <c r="D490" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E490" t="s">
         <v>10</v>
       </c>
       <c r="F490">
-        <v>168</v>
+        <v>228</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13312,19 +13306,19 @@
         <v>1008</v>
       </c>
       <c r="B491" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C491" t="s">
         <v>1009</v>
       </c>
       <c r="D491" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E491" t="s">
         <v>10</v>
       </c>
       <c r="F491">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13332,19 +13326,19 @@
         <v>1010</v>
       </c>
       <c r="B492" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C492" t="s">
         <v>1011</v>
       </c>
       <c r="D492" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E492" t="s">
         <v>10</v>
       </c>
       <c r="F492">
-        <v>294</v>
+        <v>279</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13352,19 +13346,19 @@
         <v>1012</v>
       </c>
       <c r="B493" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C493" t="s">
         <v>1013</v>
       </c>
       <c r="D493" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E493" t="s">
         <v>10</v>
       </c>
       <c r="F493">
-        <v>297</v>
+        <v>178</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13372,19 +13366,19 @@
         <v>1014</v>
       </c>
       <c r="B494" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C494" t="s">
         <v>1015</v>
       </c>
       <c r="D494" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E494" t="s">
         <v>10</v>
       </c>
       <c r="F494">
-        <v>186</v>
+        <v>177</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13392,19 +13386,19 @@
         <v>1016</v>
       </c>
       <c r="B495" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C495" t="s">
         <v>1017</v>
       </c>
       <c r="D495" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E495" t="s">
         <v>10</v>
       </c>
       <c r="F495">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13412,19 +13406,19 @@
         <v>1018</v>
       </c>
       <c r="B496" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C496" t="s">
         <v>1019</v>
       </c>
       <c r="D496" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E496" t="s">
         <v>10</v>
       </c>
       <c r="F496">
-        <v>184</v>
+        <v>236</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13432,19 +13426,19 @@
         <v>1020</v>
       </c>
       <c r="B497" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C497" t="s">
         <v>1021</v>
       </c>
       <c r="D497" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E497" t="s">
         <v>10</v>
       </c>
       <c r="F497">
-        <v>234</v>
+        <v>166</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13452,19 +13446,19 @@
         <v>1022</v>
       </c>
       <c r="B498" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C498" t="s">
         <v>1023</v>
       </c>
       <c r="D498" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E498" t="s">
         <v>10</v>
       </c>
       <c r="F498">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -13472,19 +13466,19 @@
         <v>1024</v>
       </c>
       <c r="B499" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C499" t="s">
         <v>1025</v>
       </c>
       <c r="D499" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E499" t="s">
         <v>10</v>
       </c>
       <c r="F499">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -13492,19 +13486,19 @@
         <v>1026</v>
       </c>
       <c r="B500" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C500" t="s">
         <v>1027</v>
       </c>
       <c r="D500" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E500" t="s">
         <v>10</v>
       </c>
       <c r="F500">
-        <v>214</v>
+        <v>134</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -13512,39 +13506,19 @@
         <v>1028</v>
       </c>
       <c r="B501" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C501" t="s">
         <v>1029</v>
       </c>
       <c r="D501" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E501" t="s">
         <v>10</v>
       </c>
       <c r="F501">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B502" t="s">
-        <v>934</v>
-      </c>
-      <c r="C502" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D502" t="s">
-        <v>13</v>
-      </c>
-      <c r="E502" t="s">
-        <v>10</v>
-      </c>
-      <c r="F502">
-        <v>166</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
